--- a/reports-samples/ar-aging-report.xlsx
+++ b/reports-samples/ar-aging-report.xlsx
@@ -25,7 +25,7 @@
     <t>current</t>
   </si>
   <si>
-    <t>35751.50</t>
+    <t>30254.50</t>
   </si>
   <si>
     <t>1-30</t>
@@ -49,7 +49,7 @@
     <t>90+</t>
   </si>
   <si>
-    <t>4447.00</t>
+    <t>2448.00</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -503,7 +503,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
